--- a/tables/Ne_table.xlsx
+++ b/tables/Ne_table.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/51a2c13cefa91c23/Documents/R Working Directory/Bison_github/tables/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\R_WD\woodbison\tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="41" documentId="14_{4825CC58-3770-4696-97A8-510F4238C4D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2588C5E0-CFD0-4C94-8848-254476E9014A}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EB5DA3C-1A4B-460B-A3FD-51F5A807630E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5040" yWindow="367" windowWidth="10263" windowHeight="12802" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="49">
   <si>
     <t>Population</t>
   </si>
@@ -236,13 +236,94 @@
       <t>a</t>
     </r>
   </si>
+  <si>
+    <r>
+      <t>Estimated Effective Population Size (N</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>e</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">N </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>(Year)</t>
+    </r>
+  </si>
+  <si>
+    <t>~740 (1993)</t>
+  </si>
+  <si>
+    <t>300 (2019)</t>
+  </si>
+  <si>
+    <t>1,906 (2025)</t>
+  </si>
+  <si>
+    <t>982 (2024)</t>
+  </si>
+  <si>
+    <t>424 (2024)</t>
+  </si>
+  <si>
+    <t>101 (2024)</t>
+  </si>
+  <si>
+    <t>282 (2024)</t>
+  </si>
+  <si>
+    <t>642 (2024)</t>
+  </si>
+  <si>
+    <t>199 (2016)</t>
+  </si>
+  <si>
+    <t>8 (2025)</t>
+  </si>
+  <si>
+    <t>186 (2013)</t>
+  </si>
+  <si>
+    <t>15 (2014)</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="0.000000"/>
+    <numFmt numFmtId="164" formatCode="0.000000"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
@@ -324,7 +405,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -332,23 +413,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -362,13 +434,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -377,22 +446,31 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -416,7 +494,7 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>19</xdr:col>
+      <xdr:col>20</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
       <xdr:row>3</xdr:row>
       <xdr:rowOff>90487</xdr:rowOff>
@@ -735,1233 +813,1290 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:P31"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A2:Q31"/>
+  <sheetFormatPr defaultRowHeight="15.05" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.7109375" customWidth="1"/>
-    <col min="2" max="2" width="11.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.6640625" customWidth="1"/>
+    <col min="2" max="2" width="11.6640625" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="29.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="22.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.88671875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.33203125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="14" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.85546875" customWidth="1"/>
-    <col min="15" max="15" width="12.140625" customWidth="1"/>
-    <col min="16" max="16" width="17.42578125" customWidth="1"/>
+    <col min="11" max="11" width="12.88671875" customWidth="1"/>
+    <col min="15" max="15" width="12.109375" customWidth="1"/>
+    <col min="16" max="16" width="12.109375" style="22" customWidth="1"/>
+    <col min="17" max="17" width="17.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:16" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="10"/>
-      <c r="B2" s="7" t="s">
+    <row r="2" spans="1:17" ht="17.7" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="7"/>
+      <c r="B2" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="D2" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="E2" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="F2" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="G2" s="8" t="s">
+      <c r="G2" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="H2" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="I2" s="8" t="s">
+      <c r="I2" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="J2" s="8" t="s">
+      <c r="J2" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="K2" s="8" t="s">
+      <c r="K2" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="N2" s="10"/>
-      <c r="O2" s="7" t="s">
+      <c r="N2" s="7"/>
+      <c r="O2" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="P2" s="8" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+      <c r="P2" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q2" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A3" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="5">
+      <c r="C3" s="1">
         <v>30</v>
       </c>
-      <c r="D3" s="5">
+      <c r="D3" s="1">
         <v>30</v>
       </c>
-      <c r="E3" s="5">
+      <c r="E3" s="1">
         <v>12561</v>
       </c>
-      <c r="F3" s="18">
+      <c r="F3" s="14">
         <v>3.8792E-2</v>
       </c>
-      <c r="G3" s="18">
+      <c r="G3" s="14">
         <v>3.6878000000000001E-2</v>
       </c>
-      <c r="H3" s="5">
+      <c r="H3" s="1">
         <v>159.19999999999999</v>
       </c>
-      <c r="I3" s="5">
+      <c r="I3" s="1">
         <v>86.6</v>
       </c>
-      <c r="J3" s="5">
+      <c r="J3" s="1">
         <v>713.8</v>
       </c>
       <c r="K3" s="1">
         <v>4955</v>
       </c>
-      <c r="N3" s="3" t="s">
+      <c r="N3" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="O3" s="4" t="s">
+      <c r="O3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P3" s="5">
+      <c r="P3" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q3" s="1">
         <v>159.19999999999999</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A4" s="3"/>
-      <c r="B4" s="14" t="s">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A4" s="19"/>
+      <c r="B4" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="15">
+      <c r="C4" s="11">
         <v>39</v>
       </c>
-      <c r="D4" s="15">
+      <c r="D4" s="11">
         <v>39</v>
       </c>
-      <c r="E4" s="15">
+      <c r="E4" s="11">
         <v>10332</v>
       </c>
-      <c r="F4" s="19">
+      <c r="F4" s="15">
         <v>3.4429000000000001E-2</v>
       </c>
-      <c r="G4" s="19">
+      <c r="G4" s="15">
         <v>2.7737999999999999E-2</v>
       </c>
-      <c r="H4" s="15">
+      <c r="H4" s="11">
         <v>47.7</v>
       </c>
-      <c r="I4" s="15">
+      <c r="I4" s="11">
         <v>27</v>
       </c>
-      <c r="J4" s="15">
+      <c r="J4" s="11">
         <v>117.9</v>
       </c>
-      <c r="K4" s="23">
+      <c r="K4" s="11">
         <v>496</v>
       </c>
-      <c r="N4" s="3"/>
-      <c r="O4" s="14" t="s">
+      <c r="N4" s="19"/>
+      <c r="O4" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="P4" s="15">
+      <c r="P4" s="11"/>
+      <c r="Q4" s="11">
         <v>47.7</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A5" s="3"/>
-      <c r="B5" s="4" t="s">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A5" s="19"/>
+      <c r="B5" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="5">
+      <c r="C5" s="1">
         <v>28</v>
       </c>
-      <c r="D5" s="5">
+      <c r="D5" s="1">
         <v>28</v>
       </c>
-      <c r="E5" s="5">
+      <c r="E5" s="1">
         <v>10909</v>
       </c>
-      <c r="F5" s="18">
+      <c r="F5" s="14">
         <v>4.0478E-2</v>
       </c>
-      <c r="G5" s="18">
+      <c r="G5" s="14">
         <v>3.9856000000000003E-2</v>
       </c>
-      <c r="H5" s="5">
+      <c r="H5" s="1">
         <v>493.8</v>
       </c>
-      <c r="I5" s="5">
+      <c r="I5" s="1">
         <v>114.7</v>
       </c>
-      <c r="J5" s="5" t="s">
+      <c r="J5" s="1" t="s">
         <v>5</v>
       </c>
       <c r="K5" s="1">
         <v>3309</v>
       </c>
-      <c r="N5" s="3"/>
-      <c r="O5" s="4" t="s">
+      <c r="N5" s="19"/>
+      <c r="O5" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P5" s="5">
+      <c r="P5" s="1"/>
+      <c r="Q5" s="1">
         <v>493.8</v>
       </c>
     </row>
-    <row r="6" spans="1:16" ht="18" x14ac:dyDescent="0.25">
-      <c r="A6" s="3"/>
-      <c r="B6" s="14" t="s">
+    <row r="6" spans="1:17" ht="17.05" x14ac:dyDescent="0.3">
+      <c r="A6" s="19"/>
+      <c r="B6" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="15">
+      <c r="C6" s="11">
         <v>10</v>
       </c>
-      <c r="D6" s="15">
+      <c r="D6" s="11">
         <v>10</v>
       </c>
-      <c r="E6" s="15">
+      <c r="E6" s="11">
         <v>11343</v>
       </c>
-      <c r="F6" s="19">
+      <c r="F6" s="15">
         <v>0.13459599999999999</v>
       </c>
-      <c r="G6" s="19">
+      <c r="G6" s="15">
         <v>0.13711599999999999</v>
       </c>
-      <c r="H6" s="15">
+      <c r="H6" s="11">
         <v>-123.9</v>
       </c>
-      <c r="I6" s="15">
+      <c r="I6" s="11">
         <v>266.2</v>
       </c>
-      <c r="J6" s="15" t="s">
+      <c r="J6" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="K6" s="23">
+      <c r="K6" s="11">
         <v>10765</v>
       </c>
-      <c r="N6" s="3"/>
-      <c r="O6" s="14" t="s">
+      <c r="N6" s="19"/>
+      <c r="O6" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="P6" s="15" t="s">
+      <c r="P6" s="11"/>
+      <c r="Q6" s="11" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A7" s="3"/>
-      <c r="B7" s="4" t="s">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A7" s="19"/>
+      <c r="B7" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="5">
+      <c r="C7" s="1">
         <v>23</v>
       </c>
-      <c r="D7" s="5">
+      <c r="D7" s="1">
         <v>23</v>
       </c>
-      <c r="E7" s="5">
+      <c r="E7" s="1">
         <v>13037</v>
       </c>
-      <c r="F7" s="18">
+      <c r="F7" s="14">
         <v>5.0462E-2</v>
       </c>
-      <c r="G7" s="18">
+      <c r="G7" s="14">
         <v>4.9738999999999998E-2</v>
       </c>
-      <c r="H7" s="5">
+      <c r="H7" s="1">
         <v>424.1</v>
       </c>
-      <c r="I7" s="5">
+      <c r="I7" s="1">
         <v>105.1</v>
       </c>
-      <c r="J7" s="5" t="s">
+      <c r="J7" s="1" t="s">
         <v>5</v>
       </c>
       <c r="K7" s="1">
         <v>4461</v>
       </c>
-      <c r="N7" s="3"/>
-      <c r="O7" s="4" t="s">
+      <c r="N7" s="19"/>
+      <c r="O7" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="P7" s="5">
+      <c r="P7" s="1"/>
+      <c r="Q7" s="1">
         <v>424.1</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A8" s="3"/>
-      <c r="B8" s="14" t="s">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A8" s="19"/>
+      <c r="B8" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="15">
+      <c r="C8" s="11">
         <v>11</v>
       </c>
-      <c r="D8" s="15">
+      <c r="D8" s="11">
         <v>10.8</v>
       </c>
-      <c r="E8" s="15">
+      <c r="E8" s="11">
         <v>8263</v>
       </c>
-      <c r="F8" s="19">
+      <c r="F8" s="15">
         <v>0.12846399999999999</v>
       </c>
-      <c r="G8" s="19">
+      <c r="G8" s="15">
         <v>0.123295</v>
       </c>
-      <c r="H8" s="15">
+      <c r="H8" s="11">
         <v>57.8</v>
       </c>
-      <c r="I8" s="15">
+      <c r="I8" s="11">
         <v>10.8</v>
       </c>
-      <c r="J8" s="15" t="s">
+      <c r="J8" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="K8" s="23">
+      <c r="K8" s="11">
         <v>435</v>
       </c>
-      <c r="N8" s="3"/>
-      <c r="O8" s="14" t="s">
+      <c r="N8" s="19"/>
+      <c r="O8" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="P8" s="15">
+      <c r="P8" s="11"/>
+      <c r="Q8" s="11">
         <v>57.8</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A9" s="3"/>
-      <c r="B9" s="4" t="s">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A9" s="19"/>
+      <c r="B9" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="5">
+      <c r="C9" s="1">
         <v>13</v>
       </c>
-      <c r="D9" s="5">
+      <c r="D9" s="1">
         <v>13</v>
       </c>
-      <c r="E9" s="5">
+      <c r="E9" s="1">
         <v>9102</v>
       </c>
-      <c r="F9" s="18">
+      <c r="F9" s="14">
         <v>0.10149900000000001</v>
       </c>
-      <c r="G9" s="18">
+      <c r="G9" s="14">
         <v>9.7840999999999997E-2</v>
       </c>
-      <c r="H9" s="5">
+      <c r="H9" s="1">
         <v>82.5</v>
       </c>
-      <c r="I9" s="5">
+      <c r="I9" s="1">
         <v>28.8</v>
       </c>
-      <c r="J9" s="5" t="s">
+      <c r="J9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="K9" s="1">
         <v>2113</v>
       </c>
-      <c r="N9" s="3"/>
-      <c r="O9" s="4" t="s">
+      <c r="N9" s="19"/>
+      <c r="O9" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="P9" s="5">
+      <c r="P9" s="1"/>
+      <c r="Q9" s="1">
         <v>82.5</v>
       </c>
     </row>
-    <row r="10" spans="1:16" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="6"/>
-      <c r="B10" s="16" t="s">
+    <row r="10" spans="1:17" ht="17.7" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="20"/>
+      <c r="B10" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="17">
+      <c r="C10" s="13">
         <v>24</v>
       </c>
-      <c r="D10" s="17">
+      <c r="D10" s="13">
         <v>24</v>
       </c>
-      <c r="E10" s="17">
+      <c r="E10" s="13">
         <v>13517</v>
       </c>
-      <c r="F10" s="20">
+      <c r="F10" s="16">
         <v>4.7280999999999997E-2</v>
       </c>
-      <c r="G10" s="20">
+      <c r="G10" s="16">
         <v>4.7300000000000002E-2</v>
       </c>
-      <c r="H10" s="17">
+      <c r="H10" s="13">
         <v>-16219.7</v>
       </c>
-      <c r="I10" s="17">
+      <c r="I10" s="13">
         <v>156.6</v>
       </c>
-      <c r="J10" s="17" t="s">
+      <c r="J10" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="K10" s="17">
+      <c r="K10" s="13">
         <v>4730</v>
       </c>
-      <c r="N10" s="6"/>
-      <c r="O10" s="16" t="s">
+      <c r="N10" s="20"/>
+      <c r="O10" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="P10" s="17" t="s">
+      <c r="P10" s="13"/>
+      <c r="Q10" s="13" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A11" s="11" t="s">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A11" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="B11" s="12" t="s">
+      <c r="B11" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C11" s="13">
+      <c r="C11" s="8">
         <v>33</v>
       </c>
-      <c r="D11" s="13">
+      <c r="D11" s="8">
         <v>33</v>
       </c>
-      <c r="E11" s="13">
+      <c r="E11" s="8">
         <v>9251</v>
       </c>
-      <c r="F11" s="21">
+      <c r="F11" s="17">
         <v>3.9935999999999999E-2</v>
       </c>
-      <c r="G11" s="21">
+      <c r="G11" s="17">
         <v>3.3231999999999998E-2</v>
       </c>
-      <c r="H11" s="13">
+      <c r="H11" s="8">
         <v>47.6</v>
       </c>
-      <c r="I11" s="13">
+      <c r="I11" s="8">
         <v>29.9</v>
       </c>
-      <c r="J11" s="13">
+      <c r="J11" s="8">
         <v>93.7</v>
       </c>
       <c r="K11" s="1">
         <v>1037</v>
       </c>
-      <c r="N11" s="11" t="s">
+      <c r="N11" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="O11" s="12" t="s">
+      <c r="O11" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="P11" s="13">
+      <c r="P11" s="8"/>
+      <c r="Q11" s="8">
         <v>47.6</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A12" s="3"/>
-      <c r="B12" s="14" t="s">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A12" s="19"/>
+      <c r="B12" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C12" s="15">
+      <c r="C12" s="11">
         <v>51</v>
       </c>
-      <c r="D12" s="15">
+      <c r="D12" s="11">
         <v>50.9</v>
       </c>
-      <c r="E12" s="15">
+      <c r="E12" s="11">
         <v>9964</v>
       </c>
-      <c r="F12" s="19">
+      <c r="F12" s="15">
         <v>2.094E-2</v>
       </c>
-      <c r="G12" s="19">
+      <c r="G12" s="15">
         <v>2.0858000000000002E-2</v>
       </c>
-      <c r="H12" s="15">
+      <c r="H12" s="11">
         <v>4090.5</v>
       </c>
-      <c r="I12" s="15">
+      <c r="I12" s="11">
         <v>351.1</v>
       </c>
-      <c r="J12" s="15" t="s">
+      <c r="J12" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="K12" s="23">
+      <c r="K12" s="11">
         <v>4815</v>
       </c>
-      <c r="N12" s="3"/>
-      <c r="O12" s="14" t="s">
+      <c r="N12" s="19"/>
+      <c r="O12" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="P12" s="15">
+      <c r="P12" s="11"/>
+      <c r="Q12" s="11">
         <v>4090.5</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A13" s="3"/>
-      <c r="B13" s="4" t="s">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A13" s="19"/>
+      <c r="B13" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C13" s="5">
+      <c r="C13" s="1">
         <v>19</v>
       </c>
-      <c r="D13" s="5">
+      <c r="D13" s="1">
         <v>19</v>
       </c>
-      <c r="E13" s="5">
+      <c r="E13" s="1">
         <v>7833</v>
       </c>
-      <c r="F13" s="18">
+      <c r="F13" s="14">
         <v>7.1138999999999994E-2</v>
       </c>
-      <c r="G13" s="18">
+      <c r="G13" s="14">
         <v>6.1836000000000002E-2</v>
       </c>
-      <c r="H13" s="5">
+      <c r="H13" s="1">
         <v>31.3</v>
       </c>
-      <c r="I13" s="5">
+      <c r="I13" s="1">
         <v>16.5</v>
       </c>
-      <c r="J13" s="5">
+      <c r="J13" s="1">
         <v>105.8</v>
       </c>
       <c r="K13" s="1">
         <v>813</v>
       </c>
-      <c r="N13" s="3"/>
-      <c r="O13" s="4" t="s">
+      <c r="N13" s="19"/>
+      <c r="O13" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="P13" s="5">
+      <c r="P13" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q13" s="1">
         <v>31.3</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A14" s="3"/>
-      <c r="B14" s="14" t="s">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A14" s="19"/>
+      <c r="B14" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="C14" s="15">
+      <c r="C14" s="11">
         <v>10</v>
       </c>
-      <c r="D14" s="15">
+      <c r="D14" s="11">
         <v>10</v>
       </c>
-      <c r="E14" s="15">
+      <c r="E14" s="11">
         <v>5354</v>
       </c>
-      <c r="F14" s="19">
+      <c r="F14" s="15">
         <v>0.15074499999999999</v>
       </c>
-      <c r="G14" s="19">
+      <c r="G14" s="15">
         <v>0.13689999999999999</v>
       </c>
-      <c r="H14" s="15">
+      <c r="H14" s="11">
         <v>20.399999999999999</v>
       </c>
-      <c r="I14" s="15">
+      <c r="I14" s="11">
         <v>8.9</v>
       </c>
-      <c r="J14" s="15">
+      <c r="J14" s="11">
         <v>223.3</v>
       </c>
-      <c r="K14" s="23">
+      <c r="K14" s="11">
         <v>985</v>
       </c>
-      <c r="N14" s="3"/>
-      <c r="O14" s="14" t="s">
+      <c r="N14" s="19"/>
+      <c r="O14" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="P14" s="15">
+      <c r="P14" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q14" s="11">
         <v>20.399999999999999</v>
       </c>
     </row>
-    <row r="15" spans="1:16" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="6"/>
-      <c r="B15" s="7" t="s">
+    <row r="15" spans="1:17" ht="17.7" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="20"/>
+      <c r="B15" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C15" s="8">
+      <c r="C15" s="4">
         <v>5</v>
       </c>
-      <c r="D15" s="8">
+      <c r="D15" s="4">
         <v>5</v>
       </c>
-      <c r="E15" s="8">
+      <c r="E15" s="4">
         <v>5277</v>
       </c>
-      <c r="F15" s="22">
+      <c r="F15" s="18">
         <v>0.35294199999999998</v>
       </c>
-      <c r="G15" s="22">
+      <c r="G15" s="18">
         <v>0.36080000000000001</v>
       </c>
-      <c r="H15" s="8">
+      <c r="H15" s="4">
         <v>-40.799999999999997</v>
       </c>
-      <c r="I15" s="8">
+      <c r="I15" s="4">
         <v>14.9</v>
       </c>
-      <c r="J15" s="8" t="s">
+      <c r="J15" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="K15" s="8">
+      <c r="K15" s="4">
         <v>1549</v>
       </c>
-      <c r="N15" s="6"/>
-      <c r="O15" s="7" t="s">
+      <c r="N15" s="20"/>
+      <c r="O15" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="P15" s="8" t="s">
+      <c r="P15" s="4"/>
+      <c r="Q15" s="4" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A16" s="11" t="s">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A16" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="B16" s="12" t="s">
+      <c r="B16" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C16" s="13">
+      <c r="C16" s="8">
         <v>63</v>
       </c>
-      <c r="D16" s="13">
+      <c r="D16" s="8">
         <v>62.7</v>
       </c>
-      <c r="E16" s="13">
+      <c r="E16" s="8">
         <v>9235</v>
       </c>
-      <c r="F16" s="21">
+      <c r="F16" s="17">
         <v>1.7762E-2</v>
       </c>
-      <c r="G16" s="21">
+      <c r="G16" s="17">
         <v>1.6761999999999999E-2</v>
       </c>
-      <c r="H16" s="13">
+      <c r="H16" s="8">
         <v>331.5</v>
       </c>
-      <c r="I16" s="13">
+      <c r="I16" s="8">
         <v>151.19999999999999</v>
       </c>
-      <c r="J16" s="13" t="s">
+      <c r="J16" s="8" t="s">
         <v>5</v>
       </c>
       <c r="K16" s="1">
         <v>1932</v>
       </c>
-      <c r="N16" s="11" t="s">
+      <c r="N16" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="O16" s="12" t="s">
+      <c r="O16" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="P16" s="13">
+      <c r="P16" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q16" s="8">
         <v>331.5</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A17" s="3"/>
-      <c r="B17" s="14" t="s">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A17" s="19"/>
+      <c r="B17" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="C17" s="15">
+      <c r="C17" s="11">
         <v>20</v>
       </c>
-      <c r="D17" s="15">
+      <c r="D17" s="11">
         <v>19.899999999999999</v>
       </c>
-      <c r="E17" s="15">
+      <c r="E17" s="11">
         <v>5883</v>
       </c>
-      <c r="F17" s="19">
+      <c r="F17" s="15">
         <v>6.2659999999999993E-2</v>
       </c>
-      <c r="G17" s="19">
+      <c r="G17" s="15">
         <v>5.8720000000000001E-2</v>
       </c>
-      <c r="H17" s="15">
+      <c r="H17" s="11">
         <v>76.5</v>
       </c>
-      <c r="I17" s="15">
+      <c r="I17" s="11">
         <v>31.9</v>
       </c>
-      <c r="J17" s="15" t="s">
+      <c r="J17" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="K17" s="23">
+      <c r="K17" s="11">
         <v>1262</v>
       </c>
-      <c r="N17" s="3"/>
-      <c r="O17" s="14" t="s">
+      <c r="N17" s="19"/>
+      <c r="O17" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="P17" s="15">
+      <c r="P17" s="11"/>
+      <c r="Q17" s="11">
         <v>76.5</v>
       </c>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A18" s="3"/>
-      <c r="B18" s="4" t="s">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A18" s="19"/>
+      <c r="B18" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C18" s="5">
+      <c r="C18" s="1">
         <v>35</v>
       </c>
-      <c r="D18" s="5">
+      <c r="D18" s="1">
         <v>34.299999999999997</v>
       </c>
-      <c r="E18" s="5">
+      <c r="E18" s="1">
         <v>12514</v>
       </c>
-      <c r="F18" s="18">
+      <c r="F18" s="14">
         <v>3.6562999999999998E-2</v>
       </c>
-      <c r="G18" s="18">
+      <c r="G18" s="14">
         <v>3.1731000000000002E-2</v>
       </c>
-      <c r="H18" s="5">
+      <c r="H18" s="1">
         <v>66.900000000000006</v>
       </c>
-      <c r="I18" s="5">
+      <c r="I18" s="1">
         <v>35.799999999999997</v>
       </c>
-      <c r="J18" s="5">
+      <c r="J18" s="1">
         <v>229.8</v>
       </c>
       <c r="K18" s="1">
         <v>770</v>
       </c>
-      <c r="N18" s="3"/>
-      <c r="O18" s="4" t="s">
+      <c r="N18" s="19"/>
+      <c r="O18" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="P18" s="5">
+      <c r="P18" s="1"/>
+      <c r="Q18" s="1">
         <v>66.900000000000006</v>
       </c>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A19" s="3"/>
-      <c r="B19" s="14" t="s">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A19" s="19"/>
+      <c r="B19" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="C19" s="15">
+      <c r="C19" s="11">
         <v>19</v>
       </c>
-      <c r="D19" s="15">
+      <c r="D19" s="11">
         <v>17.600000000000001</v>
       </c>
-      <c r="E19" s="15">
+      <c r="E19" s="11">
         <v>8879</v>
       </c>
-      <c r="F19" s="19">
+      <c r="F19" s="15">
         <v>6.4795000000000005E-2</v>
       </c>
-      <c r="G19" s="19">
+      <c r="G19" s="15">
         <v>6.3729999999999995E-2</v>
       </c>
-      <c r="H19" s="15">
+      <c r="H19" s="11">
         <v>287.39999999999998</v>
       </c>
-      <c r="I19" s="15">
+      <c r="I19" s="11">
         <v>66</v>
       </c>
-      <c r="J19" s="15" t="s">
+      <c r="J19" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="K19" s="23">
+      <c r="K19" s="11">
         <v>2878</v>
       </c>
-      <c r="N19" s="3"/>
-      <c r="O19" s="14" t="s">
+      <c r="N19" s="19"/>
+      <c r="O19" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="P19" s="15">
+      <c r="P19" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q19" s="11">
         <v>287.39999999999998</v>
       </c>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A20" s="3"/>
-      <c r="B20" s="4" t="s">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A20" s="19"/>
+      <c r="B20" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C20" s="5">
+      <c r="C20" s="1">
         <v>31</v>
       </c>
-      <c r="D20" s="5">
+      <c r="D20" s="1">
         <v>31</v>
       </c>
-      <c r="E20" s="5">
+      <c r="E20" s="1">
         <v>7960</v>
       </c>
-      <c r="F20" s="18">
+      <c r="F20" s="14">
         <v>3.8405000000000002E-2</v>
       </c>
-      <c r="G20" s="18">
+      <c r="G20" s="14">
         <v>3.5577999999999999E-2</v>
       </c>
-      <c r="H20" s="5">
+      <c r="H20" s="1">
         <v>115.8</v>
       </c>
-      <c r="I20" s="5">
+      <c r="I20" s="1">
         <v>58.2</v>
       </c>
-      <c r="J20" s="5">
+      <c r="J20" s="1">
         <v>850.5</v>
       </c>
       <c r="K20" s="1">
         <v>1729</v>
       </c>
-      <c r="N20" s="3"/>
-      <c r="O20" s="4" t="s">
+      <c r="N20" s="19"/>
+      <c r="O20" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="P20" s="5">
+      <c r="P20" s="1"/>
+      <c r="Q20" s="1">
         <v>115.8</v>
       </c>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A21" s="3"/>
-      <c r="B21" s="14" t="s">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A21" s="19"/>
+      <c r="B21" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="C21" s="15">
+      <c r="C21" s="11">
         <v>20</v>
       </c>
-      <c r="D21" s="15">
+      <c r="D21" s="11">
         <v>19.899999999999999</v>
       </c>
-      <c r="E21" s="15">
+      <c r="E21" s="11">
         <v>7008</v>
       </c>
-      <c r="F21" s="19">
+      <c r="F21" s="15">
         <v>5.9756999999999998E-2</v>
       </c>
-      <c r="G21" s="19">
+      <c r="G21" s="15">
         <v>5.8462E-2</v>
       </c>
-      <c r="H21" s="15">
+      <c r="H21" s="11">
         <v>236.2</v>
       </c>
-      <c r="I21" s="15">
+      <c r="I21" s="11">
         <v>62.7</v>
       </c>
-      <c r="J21" s="15" t="s">
+      <c r="J21" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="K21" s="23">
+      <c r="K21" s="11">
         <v>2457</v>
       </c>
-      <c r="N21" s="3"/>
-      <c r="O21" s="14" t="s">
+      <c r="N21" s="19"/>
+      <c r="O21" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="P21" s="15">
+      <c r="P21" s="11"/>
+      <c r="Q21" s="11">
         <v>236.2</v>
       </c>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A22" s="3"/>
-      <c r="B22" s="4" t="s">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A22" s="19"/>
+      <c r="B22" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C22" s="5">
+      <c r="C22" s="1">
         <v>8</v>
       </c>
-      <c r="D22" s="5">
+      <c r="D22" s="1">
         <v>7.8</v>
       </c>
-      <c r="E22" s="5">
+      <c r="E22" s="1">
         <v>6929</v>
       </c>
-      <c r="F22" s="18">
+      <c r="F22" s="14">
         <v>0.232873</v>
       </c>
-      <c r="G22" s="18">
+      <c r="G22" s="14">
         <v>0.18906200000000001</v>
       </c>
-      <c r="H22" s="5">
+      <c r="H22" s="1">
         <v>4.2</v>
       </c>
-      <c r="I22" s="5">
+      <c r="I22" s="1">
         <v>1.6</v>
       </c>
-      <c r="J22" s="5">
+      <c r="J22" s="1">
         <v>52.5</v>
       </c>
       <c r="K22" s="1">
         <v>219</v>
       </c>
-      <c r="N22" s="3"/>
-      <c r="O22" s="4" t="s">
+      <c r="N22" s="19"/>
+      <c r="O22" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="P22" s="5">
+      <c r="P22" s="1"/>
+      <c r="Q22" s="1">
         <v>4.2</v>
       </c>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A23" s="3"/>
-      <c r="B23" s="14" t="s">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A23" s="19"/>
+      <c r="B23" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="C23" s="15">
+      <c r="C23" s="11">
         <v>17</v>
       </c>
-      <c r="D23" s="15">
+      <c r="D23" s="11">
         <v>17</v>
       </c>
-      <c r="E23" s="15">
+      <c r="E23" s="11">
         <v>6100</v>
       </c>
-      <c r="F23" s="19">
+      <c r="F23" s="15">
         <v>9.0676999999999994E-2</v>
       </c>
-      <c r="G23" s="19">
+      <c r="G23" s="15">
         <v>7.0682999999999996E-2</v>
       </c>
-      <c r="H23" s="15">
+      <c r="H23" s="11">
         <v>13.5</v>
       </c>
-      <c r="I23" s="15">
+      <c r="I23" s="11">
         <v>6.2</v>
       </c>
-      <c r="J23" s="15">
+      <c r="J23" s="11">
         <v>40.6</v>
       </c>
-      <c r="K23" s="23">
+      <c r="K23" s="11">
         <v>311</v>
       </c>
-      <c r="N23" s="3"/>
-      <c r="O23" s="14" t="s">
+      <c r="N23" s="19"/>
+      <c r="O23" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="P23" s="15">
+      <c r="P23" s="11"/>
+      <c r="Q23" s="11">
         <v>13.5</v>
       </c>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A24" s="3"/>
-      <c r="B24" s="4" t="s">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A24" s="19"/>
+      <c r="B24" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C24" s="5">
+      <c r="C24" s="1">
         <v>29</v>
       </c>
-      <c r="D24" s="5">
+      <c r="D24" s="1">
         <v>29</v>
       </c>
-      <c r="E24" s="5">
+      <c r="E24" s="1">
         <v>7244</v>
       </c>
-      <c r="F24" s="18">
+      <c r="F24" s="14">
         <v>4.3445999999999999E-2</v>
       </c>
-      <c r="G24" s="18">
+      <c r="G24" s="14">
         <v>3.8355E-2</v>
       </c>
-      <c r="H24" s="5">
+      <c r="H24" s="1">
         <v>58.8</v>
       </c>
-      <c r="I24" s="5">
+      <c r="I24" s="1">
         <v>35.799999999999997</v>
       </c>
-      <c r="J24" s="5">
+      <c r="J24" s="1">
         <v>133.1</v>
       </c>
       <c r="K24" s="1">
         <v>1666</v>
       </c>
-      <c r="N24" s="3"/>
-      <c r="O24" s="4" t="s">
+      <c r="N24" s="19"/>
+      <c r="O24" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="P24" s="5">
+      <c r="P24" s="1"/>
+      <c r="Q24" s="1">
         <v>58.8</v>
       </c>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A25" s="3"/>
-      <c r="B25" s="14" t="s">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A25" s="19"/>
+      <c r="B25" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="C25" s="15">
+      <c r="C25" s="11">
         <v>8</v>
       </c>
-      <c r="D25" s="15">
+      <c r="D25" s="11">
         <v>8</v>
       </c>
-      <c r="E25" s="15">
+      <c r="E25" s="11">
         <v>4189</v>
       </c>
-      <c r="F25" s="19">
+      <c r="F25" s="15">
         <v>0.206681</v>
       </c>
-      <c r="G25" s="19">
+      <c r="G25" s="15">
         <v>0.18574599999999999</v>
       </c>
-      <c r="H25" s="15">
+      <c r="H25" s="11">
         <v>12.8</v>
       </c>
-      <c r="I25" s="15">
+      <c r="I25" s="11">
         <v>5.4</v>
       </c>
-      <c r="J25" s="15">
+      <c r="J25" s="11">
         <v>61.8</v>
       </c>
-      <c r="K25" s="23">
+      <c r="K25" s="11">
         <v>1123</v>
       </c>
-      <c r="N25" s="3"/>
-      <c r="O25" s="14" t="s">
+      <c r="N25" s="19"/>
+      <c r="O25" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="P25" s="15">
+      <c r="P25" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q25" s="11">
         <v>12.8</v>
       </c>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A26" s="3"/>
-      <c r="B26" s="4" t="s">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A26" s="19"/>
+      <c r="B26" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C26" s="5">
+      <c r="C26" s="1">
         <v>21</v>
       </c>
-      <c r="D26" s="5">
+      <c r="D26" s="1">
         <v>20.9</v>
       </c>
-      <c r="E26" s="5">
+      <c r="E26" s="1">
         <v>11839</v>
       </c>
-      <c r="F26" s="18">
+      <c r="F26" s="14">
         <v>5.5503999999999998E-2</v>
       </c>
-      <c r="G26" s="18">
+      <c r="G26" s="14">
         <v>5.5370999999999997E-2</v>
       </c>
-      <c r="H26" s="5">
+      <c r="H26" s="1">
         <v>2320.5</v>
       </c>
-      <c r="I26" s="5">
+      <c r="I26" s="1">
         <v>110.5</v>
       </c>
-      <c r="J26" s="5" t="s">
+      <c r="J26" s="1" t="s">
         <v>5</v>
       </c>
       <c r="K26" s="1">
         <v>3715</v>
       </c>
-      <c r="N26" s="3"/>
-      <c r="O26" s="4" t="s">
+      <c r="N26" s="19"/>
+      <c r="O26" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="P26" s="5">
+      <c r="P26" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q26" s="1">
         <v>2320.5</v>
       </c>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A27" s="3"/>
-      <c r="B27" s="14" t="s">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A27" s="19"/>
+      <c r="B27" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="C27" s="15">
+      <c r="C27" s="11">
         <v>30</v>
       </c>
-      <c r="D27" s="15">
+      <c r="D27" s="11">
         <v>29.6</v>
       </c>
-      <c r="E27" s="15">
+      <c r="E27" s="11">
         <v>13805</v>
       </c>
-      <c r="F27" s="19">
+      <c r="F27" s="15">
         <v>3.8859999999999999E-2</v>
       </c>
-      <c r="G27" s="19">
+      <c r="G27" s="15">
         <v>3.7304999999999998E-2</v>
       </c>
-      <c r="H27" s="15">
+      <c r="H27" s="11">
         <v>196.4</v>
       </c>
-      <c r="I27" s="15">
+      <c r="I27" s="11">
         <v>70.2</v>
       </c>
-      <c r="J27" s="15" t="s">
+      <c r="J27" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="K27" s="23">
+      <c r="K27" s="11">
         <v>1729</v>
       </c>
-      <c r="N27" s="3"/>
-      <c r="O27" s="14" t="s">
+      <c r="N27" s="19"/>
+      <c r="O27" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="P27" s="15">
+      <c r="P27" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q27" s="11">
         <v>196.4</v>
       </c>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A28" s="3"/>
-      <c r="B28" s="4" t="s">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A28" s="19"/>
+      <c r="B28" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C28" s="5">
+      <c r="C28" s="1">
         <v>25</v>
       </c>
-      <c r="D28" s="5">
+      <c r="D28" s="1">
         <v>24.7</v>
       </c>
-      <c r="E28" s="5">
+      <c r="E28" s="1">
         <v>11134</v>
       </c>
-      <c r="F28" s="18">
+      <c r="F28" s="14">
         <v>4.8737999999999997E-2</v>
       </c>
-      <c r="G28" s="18">
+      <c r="G28" s="14">
         <v>4.5754000000000003E-2</v>
       </c>
-      <c r="H28" s="5">
+      <c r="H28" s="1">
         <v>101.5</v>
       </c>
-      <c r="I28" s="5">
+      <c r="I28" s="1">
         <v>35.4</v>
       </c>
-      <c r="J28" s="5" t="s">
+      <c r="J28" s="1" t="s">
         <v>5</v>
       </c>
       <c r="K28" s="1">
         <v>757</v>
       </c>
-      <c r="N28" s="3"/>
-      <c r="O28" s="4" t="s">
+      <c r="N28" s="19"/>
+      <c r="O28" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P28" s="5">
+      <c r="P28" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q28" s="1">
         <v>101.5</v>
       </c>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A29" s="3"/>
-      <c r="B29" s="14" t="s">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A29" s="19"/>
+      <c r="B29" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="C29" s="15">
+      <c r="C29" s="11">
         <v>32</v>
       </c>
-      <c r="D29" s="15">
+      <c r="D29" s="11">
         <v>31.5</v>
       </c>
-      <c r="E29" s="15">
+      <c r="E29" s="11">
         <v>11120</v>
       </c>
-      <c r="F29" s="19">
+      <c r="F29" s="15">
         <v>3.7668E-2</v>
       </c>
-      <c r="G29" s="19">
+      <c r="G29" s="15">
         <v>3.4923999999999997E-2</v>
       </c>
-      <c r="H29" s="15">
+      <c r="H29" s="11">
         <v>119.4</v>
       </c>
-      <c r="I29" s="15">
+      <c r="I29" s="11">
         <v>64.599999999999994</v>
       </c>
-      <c r="J29" s="15">
+      <c r="J29" s="11">
         <v>486.6</v>
       </c>
-      <c r="K29" s="23">
+      <c r="K29" s="11">
         <v>2356</v>
       </c>
-      <c r="N29" s="3"/>
-      <c r="O29" s="14" t="s">
+      <c r="N29" s="19"/>
+      <c r="O29" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="P29" s="15">
+      <c r="P29" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q29" s="11">
         <v>119.4</v>
       </c>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A30" s="3"/>
-      <c r="B30" s="4" t="s">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A30" s="19"/>
+      <c r="B30" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C30" s="5">
+      <c r="C30" s="1">
         <v>34</v>
       </c>
-      <c r="D30" s="5">
+      <c r="D30" s="1">
         <v>33.6</v>
       </c>
-      <c r="E30" s="5">
+      <c r="E30" s="1">
         <v>14825</v>
       </c>
-      <c r="F30" s="18">
+      <c r="F30" s="14">
         <v>3.3461999999999999E-2</v>
       </c>
-      <c r="G30" s="18">
+      <c r="G30" s="14">
         <v>3.2532999999999999E-2</v>
       </c>
-      <c r="H30" s="5">
+      <c r="H30" s="1">
         <v>356.9</v>
       </c>
-      <c r="I30" s="5">
+      <c r="I30" s="1">
         <v>130.80000000000001</v>
       </c>
-      <c r="J30" s="5" t="s">
+      <c r="J30" s="1" t="s">
         <v>5</v>
       </c>
       <c r="K30" s="1">
         <v>3694</v>
       </c>
-      <c r="N30" s="3"/>
-      <c r="O30" s="4" t="s">
+      <c r="N30" s="19"/>
+      <c r="O30" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P30" s="5">
+      <c r="P30" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q30" s="1">
         <v>356.9</v>
       </c>
     </row>
-    <row r="31" spans="1:16" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="6"/>
-      <c r="B31" s="16" t="s">
+    <row r="31" spans="1:17" ht="17.7" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="20"/>
+      <c r="B31" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="C31" s="17">
+      <c r="C31" s="13">
         <v>4</v>
       </c>
-      <c r="D31" s="17">
+      <c r="D31" s="13">
         <v>4</v>
       </c>
-      <c r="E31" s="17">
+      <c r="E31" s="13">
         <v>3271</v>
       </c>
-      <c r="F31" s="20">
+      <c r="F31" s="16">
         <v>0.465202</v>
       </c>
-      <c r="G31" s="20">
+      <c r="G31" s="16">
         <v>0.50933600000000001</v>
       </c>
-      <c r="H31" s="17">
+      <c r="H31" s="13">
         <v>-8.4</v>
       </c>
-      <c r="I31" s="17" t="s">
+      <c r="I31" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="J31" s="17" t="s">
+      <c r="J31" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="K31" s="17">
+      <c r="K31" s="13">
         <v>2057</v>
       </c>
-      <c r="N31" s="6"/>
-      <c r="O31" s="16" t="s">
+      <c r="N31" s="20"/>
+      <c r="O31" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="P31" s="17" t="s">
+      <c r="P31" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q31" s="13" t="s">
         <v>31</v>
       </c>
     </row>
@@ -1975,6 +2110,7 @@
     <mergeCell ref="N16:N31"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>